--- a/students dashboard/Grades/grade 4 library students names.xlsx
+++ b/students dashboard/Grades/grade 4 library students names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geofr\Desktop\Github\Adminstrators Portal\students dashboard\Grades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779C93BC-1ACD-4542-8020-1CBC7F9784E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B814A7-D895-4AE5-807D-C063439B93DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NCbaEnrollment_List_school!$A$3:$M$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">NCbaEnrollment_List_school!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="176">
   <si>
     <t/>
   </si>
@@ -540,13 +541,31 @@
     <t>"DateOfBirth":"2019",</t>
   </si>
   <si>
-    <t>"assessmentNo":"",</t>
-  </si>
-  <si>
     <t>"Status":"Active"</t>
   </si>
   <si>
     <t>"upi":"BK001",</t>
+  </si>
+  <si>
+    <t>"assessmentNo":"B006658253",</t>
+  </si>
+  <si>
+    <t>"assessmentNo":"B006400001",</t>
+  </si>
+  <si>
+    <t>"name": "CLINTON OMONDI AINDO",</t>
+  </si>
+  <si>
+    <t>"assessmentNo":"B006400002",</t>
+  </si>
+  <si>
+    <t>"assessmentNo":"B008120758",</t>
+  </si>
+  <si>
+    <t>"name": "NOAH OTIENO MBUYA",</t>
+  </si>
+  <si>
+    <t>"name": "SAMUEL ONYANGO OMONDI",</t>
   </si>
 </sst>
 </file>
@@ -564,11 +583,13 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1042,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.453125" bestFit="1" customWidth="1"/>
@@ -1079,7 +1100,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>7</v>
@@ -1100,7 +1121,7 @@
         <v>159</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>1</v>
@@ -1117,7 +1138,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -1138,7 +1159,7 @@
         <v>160</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>1</v>
@@ -1155,9 +1176,9 @@
         <v>6</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1176,7 +1197,7 @@
         <v>161</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>1</v>
@@ -1193,9 +1214,9 @@
         <v>6</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1214,7 +1235,7 @@
         <v>162</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>1</v>
@@ -1231,7 +1252,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>11</v>
@@ -1252,7 +1273,7 @@
         <v>163</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>1</v>
@@ -1269,7 +1290,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>12</v>
@@ -1290,7 +1311,7 @@
         <v>164</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>1</v>
@@ -1307,7 +1328,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>13</v>
@@ -1328,7 +1349,7 @@
         <v>159</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>1</v>
@@ -1345,7 +1366,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>14</v>
@@ -1366,7 +1387,7 @@
         <v>162</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>1</v>
@@ -1383,7 +1404,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>15</v>
@@ -1404,7 +1425,7 @@
         <v>163</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>1</v>
@@ -1421,7 +1442,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>16</v>
@@ -1442,7 +1463,7 @@
         <v>163</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>1</v>
@@ -1459,7 +1480,7 @@
         <v>6</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>17</v>
@@ -1480,7 +1501,7 @@
         <v>165</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>1</v>
@@ -1497,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>18</v>
@@ -1518,7 +1539,7 @@
         <v>159</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>1</v>
@@ -1535,7 +1556,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>19</v>
@@ -1556,7 +1577,7 @@
         <v>164</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>1</v>
@@ -1573,7 +1594,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>20</v>
@@ -1594,7 +1615,7 @@
         <v>164</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>1</v>
@@ -1611,7 +1632,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>21</v>
@@ -1632,7 +1653,7 @@
         <v>164</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>1</v>
@@ -1649,7 +1670,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>22</v>
@@ -1670,7 +1691,7 @@
         <v>164</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>1</v>
@@ -1687,7 +1708,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>23</v>
@@ -1708,7 +1729,7 @@
         <v>164</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>1</v>
@@ -1725,7 +1746,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>24</v>
@@ -1746,7 +1767,7 @@
         <v>164</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>1</v>
@@ -1763,7 +1784,7 @@
         <v>6</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>25</v>
@@ -1784,7 +1805,7 @@
         <v>159</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>1</v>
@@ -1801,7 +1822,7 @@
         <v>6</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>26</v>
@@ -1822,7 +1843,7 @@
         <v>164</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>1</v>
@@ -1839,7 +1860,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>27</v>
@@ -1860,7 +1881,7 @@
         <v>163</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>1</v>
@@ -1877,7 +1898,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>28</v>
@@ -1898,7 +1919,7 @@
         <v>159</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>1</v>
@@ -1915,7 +1936,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>29</v>
@@ -1936,7 +1957,7 @@
         <v>162</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>1</v>
@@ -1953,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>30</v>
@@ -1974,7 +1995,7 @@
         <v>164</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>1</v>
@@ -1991,7 +2012,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>31</v>
@@ -2012,7 +2033,7 @@
         <v>162</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>1</v>
@@ -2029,7 +2050,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>32</v>
@@ -2050,7 +2071,7 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>1</v>
@@ -2067,7 +2088,7 @@
         <v>6</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>33</v>
@@ -2088,7 +2109,7 @@
         <v>164</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>1</v>
@@ -2105,7 +2126,7 @@
         <v>6</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>34</v>
@@ -2126,7 +2147,7 @@
         <v>160</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>1</v>
@@ -2143,7 +2164,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>35</v>
@@ -2164,7 +2185,7 @@
         <v>159</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>1</v>
@@ -2181,7 +2202,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>36</v>
@@ -2202,7 +2223,7 @@
         <v>164</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>1</v>
@@ -2219,7 +2240,7 @@
         <v>6</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>37</v>
@@ -2240,7 +2261,7 @@
         <v>163</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>1</v>
@@ -2257,7 +2278,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>38</v>
@@ -2278,7 +2299,7 @@
         <v>162</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>1</v>
@@ -2295,7 +2316,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>39</v>
@@ -2316,7 +2337,7 @@
         <v>163</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>1</v>
@@ -2333,7 +2354,7 @@
         <v>6</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>40</v>
@@ -2354,7 +2375,7 @@
         <v>163</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>1</v>
@@ -2371,7 +2392,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>41</v>
@@ -2392,7 +2413,7 @@
         <v>163</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>1</v>
@@ -2409,7 +2430,7 @@
         <v>6</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>42</v>
@@ -2430,7 +2451,7 @@
         <v>163</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>1</v>
@@ -2447,7 +2468,7 @@
         <v>6</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>43</v>
@@ -2468,7 +2489,7 @@
         <v>163</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>1</v>
@@ -2485,7 +2506,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>44</v>
@@ -2506,7 +2527,7 @@
         <v>163</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>1</v>
@@ -2523,7 +2544,7 @@
         <v>6</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>45</v>
@@ -2544,7 +2565,7 @@
         <v>159</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>1</v>
@@ -2561,7 +2582,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>46</v>
@@ -2582,7 +2603,7 @@
         <v>163</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>1</v>
@@ -2599,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>47</v>
@@ -2620,7 +2641,7 @@
         <v>163</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>1</v>
@@ -2637,7 +2658,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>48</v>
@@ -2658,7 +2679,7 @@
         <v>163</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>1</v>
@@ -2675,7 +2696,7 @@
         <v>6</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>49</v>
@@ -2696,7 +2717,7 @@
         <v>163</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>1</v>
@@ -2713,7 +2734,7 @@
         <v>6</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>50</v>
@@ -2734,7 +2755,7 @@
         <v>163</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>1</v>
@@ -2751,7 +2772,7 @@
         <v>6</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>51</v>
@@ -2772,7 +2793,7 @@
         <v>163</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>1</v>
@@ -2789,7 +2810,7 @@
         <v>6</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>52</v>
@@ -2810,7 +2831,7 @@
         <v>163</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>1</v>
@@ -2827,7 +2848,7 @@
         <v>6</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>53</v>
@@ -2848,7 +2869,7 @@
         <v>163</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>1</v>
@@ -2865,7 +2886,7 @@
         <v>6</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>54</v>
@@ -2886,7 +2907,7 @@
         <v>163</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>1</v>
@@ -2903,7 +2924,7 @@
         <v>6</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>55</v>
@@ -2924,7 +2945,7 @@
         <v>163</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>1</v>
@@ -2941,7 +2962,7 @@
         <v>6</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>56</v>
@@ -2962,7 +2983,7 @@
         <v>163</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>1</v>
@@ -2979,7 +3000,7 @@
         <v>6</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>57</v>
@@ -3000,7 +3021,7 @@
         <v>163</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>1</v>
@@ -3017,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>58</v>
@@ -3038,7 +3059,7 @@
         <v>166</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>1</v>
@@ -3055,7 +3076,7 @@
         <v>6</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>59</v>
@@ -3076,7 +3097,7 @@
         <v>166</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>1</v>
@@ -3093,7 +3114,7 @@
         <v>6</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>60</v>
@@ -3114,7 +3135,7 @@
         <v>166</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>1</v>
@@ -3131,7 +3152,7 @@
         <v>6</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>61</v>
@@ -3152,7 +3173,7 @@
         <v>160</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>1</v>
@@ -3169,7 +3190,7 @@
         <v>6</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>62</v>
@@ -3190,7 +3211,7 @@
         <v>163</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>1</v>
@@ -3207,7 +3228,7 @@
         <v>6</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>63</v>
@@ -3228,7 +3249,7 @@
         <v>164</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>1</v>
@@ -3245,10 +3266,10 @@
         <v>6</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" t="s">
         <v>169</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>121</v>
@@ -3266,31 +3287,140 @@
         <v>164</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L60" s="9" t="s">
         <v>4</v>
       </c>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="1:13" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C61" s="4" t="s">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" t="s">
+        <v>168</v>
+      </c>
+      <c r="E61" t="s">
+        <v>170</v>
+      </c>
+      <c r="F61" t="s">
+        <v>171</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" t="s">
+        <v>172</v>
+      </c>
+      <c r="F62" t="s">
+        <v>175</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L62" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="2"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" t="s">
+        <v>173</v>
+      </c>
+      <c r="F63" t="s">
+        <v>174</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M63" s="2"/>
+    </row>
+    <row r="64" spans="1:13" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C64" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C62" s="4" t="s">
+      <c r="D64" s="4"/>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C65" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="4"/>
-      <c r="F62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="K62" s="2"/>
+      <c r="D65" s="4"/>
+      <c r="F65" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K65" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:M3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.58667007874015797" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
